--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/16.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/16.xlsx
@@ -426,13 +426,13 @@
         <v>-14.66874859409106</v>
       </c>
       <c r="E2">
-        <v>-7.6624472776523</v>
+        <v>-10.30714855371591</v>
       </c>
       <c r="F2">
-        <v>-6.076789927850498</v>
+        <v>-5.874169604390933</v>
       </c>
       <c r="G2">
-        <v>-5.809415984437738</v>
+        <v>-6.92869156799209</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.70739333079238</v>
       </c>
       <c r="E3">
-        <v>-7.969686125176702</v>
+        <v>-10.44598250984307</v>
       </c>
       <c r="F3">
-        <v>-5.690884204480112</v>
+        <v>-5.674241474990467</v>
       </c>
       <c r="G3">
-        <v>-5.859411843171811</v>
+        <v>-7.036360440565807</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.95224006507052</v>
       </c>
       <c r="E4">
-        <v>-8.924424300213843</v>
+        <v>-10.69093672586597</v>
       </c>
       <c r="F4">
-        <v>-5.918962743329913</v>
+        <v>-5.33718540573057</v>
       </c>
       <c r="G4">
-        <v>-5.61994353158863</v>
+        <v>-7.314197974949142</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.17918946851104</v>
       </c>
       <c r="E5">
-        <v>-9.949593831492283</v>
+        <v>-11.35978327985087</v>
       </c>
       <c r="F5">
-        <v>-5.750047032755455</v>
+        <v>-5.424970812874845</v>
       </c>
       <c r="G5">
-        <v>-5.496132438965427</v>
+        <v>-6.63448338591706</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-19.33831846173396</v>
       </c>
       <c r="E6">
-        <v>-9.627279693996345</v>
+        <v>-12.4352505719325</v>
       </c>
       <c r="F6">
-        <v>-5.698813337259709</v>
+        <v>-5.30534958970618</v>
       </c>
       <c r="G6">
-        <v>-6.208929309571445</v>
+        <v>-7.013587197801161</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-20.32018086388569</v>
       </c>
       <c r="E7">
-        <v>-10.02289624025444</v>
+        <v>-12.71291848418682</v>
       </c>
       <c r="F7">
-        <v>-5.724216880401361</v>
+        <v>-5.376199853667621</v>
       </c>
       <c r="G7">
-        <v>-5.079986933042421</v>
+        <v>-6.982600491553582</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-21.04749100905621</v>
       </c>
       <c r="E8">
-        <v>-11.29768431578369</v>
+        <v>-12.42392485843932</v>
       </c>
       <c r="F8">
-        <v>-5.468491579483125</v>
+        <v>-5.361231254699034</v>
       </c>
       <c r="G8">
-        <v>-5.792737456010889</v>
+        <v>-6.521736136486101</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-21.43124403722795</v>
       </c>
       <c r="E9">
-        <v>-12.2093068897938</v>
+        <v>-14.15213997940858</v>
       </c>
       <c r="F9">
-        <v>-5.091904161026831</v>
+        <v>-5.169771525257387</v>
       </c>
       <c r="G9">
-        <v>-5.803218643188222</v>
+        <v>-7.596945048367215</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-21.41799534306004</v>
       </c>
       <c r="E10">
-        <v>-12.67633747115286</v>
+        <v>-14.41025394089778</v>
       </c>
       <c r="F10">
-        <v>-5.087570971142787</v>
+        <v>-4.964560896929268</v>
       </c>
       <c r="G10">
-        <v>-5.585633037619623</v>
+        <v>-6.679940486716792</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-20.96827346457817</v>
       </c>
       <c r="E11">
-        <v>-13.50609882052631</v>
+        <v>-15.37809751971312</v>
       </c>
       <c r="F11">
-        <v>-5.139828528748393</v>
+        <v>-4.769513508266097</v>
       </c>
       <c r="G11">
-        <v>-5.27118086957195</v>
+        <v>-7.071448912736543</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-20.07784377865988</v>
       </c>
       <c r="E12">
-        <v>-13.38171522495763</v>
+        <v>-15.50052481451048</v>
       </c>
       <c r="F12">
-        <v>-5.142538946890354</v>
+        <v>-4.641774284549996</v>
       </c>
       <c r="G12">
-        <v>-4.543688487317106</v>
+        <v>-6.032533511602459</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-18.76502025397226</v>
       </c>
       <c r="E13">
-        <v>-14.73730486220574</v>
+        <v>-16.72084440467547</v>
       </c>
       <c r="F13">
-        <v>-5.061159304871927</v>
+        <v>-4.822979653912388</v>
       </c>
       <c r="G13">
-        <v>-4.583355443968654</v>
+        <v>-5.816248950430793</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-17.09037305866669</v>
       </c>
       <c r="E14">
-        <v>-15.37615933283783</v>
+        <v>-17.00050484549316</v>
       </c>
       <c r="F14">
-        <v>-4.41593730789217</v>
+        <v>-4.273529354207295</v>
       </c>
       <c r="G14">
-        <v>-4.666135635178129</v>
+        <v>-5.491368563934415</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.14034808744993</v>
       </c>
       <c r="E15">
-        <v>-14.98758909213567</v>
+        <v>-16.24491990036535</v>
       </c>
       <c r="F15">
-        <v>-4.431672975075749</v>
+        <v>-4.167615954820157</v>
       </c>
       <c r="G15">
-        <v>-3.871753680302312</v>
+        <v>-5.401652779820166</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.02722819727533</v>
       </c>
       <c r="E16">
-        <v>-15.74897501246731</v>
+        <v>-17.57194845204707</v>
       </c>
       <c r="F16">
-        <v>-4.025550945240041</v>
+        <v>-4.223751100238267</v>
       </c>
       <c r="G16">
-        <v>-3.343321090778306</v>
+        <v>-5.136415181759298</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.87333405499234</v>
       </c>
       <c r="E17">
-        <v>-16.56929902200878</v>
+        <v>-18.45448916597993</v>
       </c>
       <c r="F17">
-        <v>-4.044395475286327</v>
+        <v>-3.842729431074788</v>
       </c>
       <c r="G17">
-        <v>-2.344936698681519</v>
+        <v>-4.067694939135156</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.803025438928882</v>
       </c>
       <c r="E18">
-        <v>-16.98856778800894</v>
+        <v>-19.25715212689148</v>
       </c>
       <c r="F18">
-        <v>-3.380999097489149</v>
+        <v>-3.228222469023433</v>
       </c>
       <c r="G18">
-        <v>-2.368421708737109</v>
+        <v>-4.256286786870818</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.929549002919729</v>
       </c>
       <c r="E19">
-        <v>-18.51396614359667</v>
+        <v>-19.39052474336539</v>
       </c>
       <c r="F19">
-        <v>-3.497154431444501</v>
+        <v>-3.011123111730336</v>
       </c>
       <c r="G19">
-        <v>-2.075832383430782</v>
+        <v>-4.177459387035231</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.342421470150437</v>
       </c>
       <c r="E20">
-        <v>-20.22773090400745</v>
+        <v>-20.49582109373555</v>
       </c>
       <c r="F20">
-        <v>-2.783152260642898</v>
+        <v>-3.009863164910678</v>
       </c>
       <c r="G20">
-        <v>-2.83946268079231</v>
+        <v>-4.732336614326935</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.099863105092757</v>
       </c>
       <c r="E21">
-        <v>-19.34167609424465</v>
+        <v>-21.91029447850539</v>
       </c>
       <c r="F21">
-        <v>-2.660148813368602</v>
+        <v>-2.110592482635951</v>
       </c>
       <c r="G21">
-        <v>-3.0281074972566</v>
+        <v>-4.271306731982491</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.225506052152826</v>
       </c>
       <c r="E22">
-        <v>-19.59521176851209</v>
+        <v>-21.89546372613027</v>
       </c>
       <c r="F22">
-        <v>-2.430676960547292</v>
+        <v>-2.101694988362482</v>
       </c>
       <c r="G22">
-        <v>-2.592578747201161</v>
+        <v>-4.337623580225171</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.723683192110024</v>
       </c>
       <c r="E23">
-        <v>-19.57029157604788</v>
+        <v>-22.09145155270824</v>
       </c>
       <c r="F23">
-        <v>-2.803885468367567</v>
+        <v>-1.997825999725452</v>
       </c>
       <c r="G23">
-        <v>-2.836575885082065</v>
+        <v>-4.308742380940569</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.572379224956559</v>
       </c>
       <c r="E24">
-        <v>-20.69940769969838</v>
+        <v>-22.64906519964273</v>
       </c>
       <c r="F24">
-        <v>-1.661382922343627</v>
+        <v>-1.659238279137779</v>
       </c>
       <c r="G24">
-        <v>-2.982435210996814</v>
+        <v>-4.190506247005499</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.731769047671682</v>
       </c>
       <c r="E25">
-        <v>-20.87207841361085</v>
+        <v>-22.51764888394013</v>
       </c>
       <c r="F25">
-        <v>-2.051453677015289</v>
+        <v>-1.841927254518585</v>
       </c>
       <c r="G25">
-        <v>-2.947164658821419</v>
+        <v>-5.280973463277114</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.13848428798888</v>
       </c>
       <c r="E26">
-        <v>-22.05900503644328</v>
+        <v>-22.77600738302574</v>
       </c>
       <c r="F26">
-        <v>-1.833592221711616</v>
+        <v>-1.687592466968203</v>
       </c>
       <c r="G26">
-        <v>-3.176724507605562</v>
+        <v>-4.940848014572392</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.725093411723761</v>
       </c>
       <c r="E27">
-        <v>-21.49373826843583</v>
+        <v>-23.34702984149694</v>
       </c>
       <c r="F27">
-        <v>-1.654217544309411</v>
+        <v>-1.61541598679488</v>
       </c>
       <c r="G27">
-        <v>-4.428908562925034</v>
+        <v>-4.916131481576193</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.421065729864745</v>
       </c>
       <c r="E28">
-        <v>-22.12582267042646</v>
+        <v>-23.40317839071805</v>
       </c>
       <c r="F28">
-        <v>-1.683463055465248</v>
+        <v>-1.780000164220099</v>
       </c>
       <c r="G28">
-        <v>-4.582408627944422</v>
+        <v>-5.240233889870843</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.170284753116162</v>
       </c>
       <c r="E29">
-        <v>-22.0073577903858</v>
+        <v>-22.74148229719126</v>
       </c>
       <c r="F29">
-        <v>-1.547690324676798</v>
+        <v>-1.845371606179425</v>
       </c>
       <c r="G29">
-        <v>-3.6483249618569</v>
+        <v>-4.738497539575519</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.92940649010216</v>
       </c>
       <c r="E30">
-        <v>-21.58159972113265</v>
+        <v>-23.71807488778942</v>
       </c>
       <c r="F30">
-        <v>-1.93516331917328</v>
+        <v>-1.678762070454361</v>
       </c>
       <c r="G30">
-        <v>-4.380955310788692</v>
+        <v>-5.284072133901872</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.669243931623785</v>
       </c>
       <c r="E31">
-        <v>-21.07212375289969</v>
+        <v>-23.33414180447111</v>
       </c>
       <c r="F31">
-        <v>-1.933403038442332</v>
+        <v>-2.081199522082417</v>
       </c>
       <c r="G31">
-        <v>-4.648801618734506</v>
+        <v>-4.986457400466931</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.367353821983126</v>
       </c>
       <c r="E32">
-        <v>-21.41893693477713</v>
+        <v>-23.12610370855874</v>
       </c>
       <c r="F32">
-        <v>-2.166814606631357</v>
+        <v>-2.192737536134564</v>
       </c>
       <c r="G32">
-        <v>-4.626531578891829</v>
+        <v>-4.936577410826732</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.007116493366295</v>
       </c>
       <c r="E33">
-        <v>-20.35833662286268</v>
+        <v>-22.73412805540281</v>
       </c>
       <c r="F33">
-        <v>-2.301860030840149</v>
+        <v>-1.926942601067898</v>
       </c>
       <c r="G33">
-        <v>-3.904892241150416</v>
+        <v>-4.274650382977154</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.578494463588992</v>
       </c>
       <c r="E34">
-        <v>-19.58048064256514</v>
+        <v>-22.25161009293751</v>
       </c>
       <c r="F34">
-        <v>-2.35583810754137</v>
+        <v>-2.114644027603044</v>
       </c>
       <c r="G34">
-        <v>-3.891421631351122</v>
+        <v>-4.115721023273363</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.073381306761947</v>
       </c>
       <c r="E35">
-        <v>-19.61160031594585</v>
+        <v>-21.57844790322331</v>
       </c>
       <c r="F35">
-        <v>-2.013652787323339</v>
+        <v>-2.076164705008201</v>
       </c>
       <c r="G35">
-        <v>-3.959605627277951</v>
+        <v>-4.201940871298142</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.487884429372782</v>
       </c>
       <c r="E36">
-        <v>-19.90957843412457</v>
+        <v>-22.15865410698207</v>
       </c>
       <c r="F36">
-        <v>-1.958621027285757</v>
+        <v>-2.341079913893094</v>
       </c>
       <c r="G36">
-        <v>-2.566425437440918</v>
+        <v>-4.045752643300866</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.817859285478203</v>
       </c>
       <c r="E37">
-        <v>-19.71041614726722</v>
+        <v>-21.34347897238732</v>
       </c>
       <c r="F37">
-        <v>-2.072274691684655</v>
+        <v>-2.225732238155472</v>
       </c>
       <c r="G37">
-        <v>-3.341086472539298</v>
+        <v>-3.773499999242282</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.06315097411254</v>
       </c>
       <c r="E38">
-        <v>-19.64444986639749</v>
+        <v>-21.33385596512102</v>
       </c>
       <c r="F38">
-        <v>-1.849048729080452</v>
+        <v>-2.191729413005358</v>
       </c>
       <c r="G38">
-        <v>-2.854479315358444</v>
+        <v>-3.224227525548564</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.21979385340804</v>
       </c>
       <c r="E39">
-        <v>-18.9782660551291</v>
+        <v>-21.39640777658897</v>
       </c>
       <c r="F39">
-        <v>-2.045983967054604</v>
+        <v>-2.282631966686367</v>
       </c>
       <c r="G39">
-        <v>-3.101727408958912</v>
+        <v>-2.982220025536762</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.28484152344298</v>
       </c>
       <c r="E40">
-        <v>-18.23387096927424</v>
+        <v>-21.16467217619445</v>
       </c>
       <c r="F40">
-        <v>-2.321990187095579</v>
+        <v>-2.321992672197788</v>
       </c>
       <c r="G40">
-        <v>-2.02669395599138</v>
+        <v>-2.981346041514394</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.25591170099781</v>
       </c>
       <c r="E41">
-        <v>-17.81440747889175</v>
+        <v>-21.27062941102592</v>
       </c>
       <c r="F41">
-        <v>-1.998559104876929</v>
+        <v>-2.236682426853078</v>
       </c>
       <c r="G41">
-        <v>-1.952620499550187</v>
+        <v>-2.519415690783267</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.13470414413735</v>
       </c>
       <c r="E42">
-        <v>-17.4619155906087</v>
+        <v>-20.31390323589941</v>
       </c>
       <c r="F42">
-        <v>-2.375583901321902</v>
+        <v>-2.46256827718767</v>
       </c>
       <c r="G42">
-        <v>-2.143754846260009</v>
+        <v>-2.475190112924144</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.925031890560257</v>
       </c>
       <c r="E43">
-        <v>-17.41659009426593</v>
+        <v>-19.89096187747903</v>
       </c>
       <c r="F43">
-        <v>-2.331470023653217</v>
+        <v>-2.431444028762284</v>
       </c>
       <c r="G43">
-        <v>-1.960317517928992</v>
+        <v>-2.040426098888277</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.632437801803974</v>
       </c>
       <c r="E44">
-        <v>-16.83665107047362</v>
+        <v>-18.94286244533714</v>
       </c>
       <c r="F44">
-        <v>-1.845242380864589</v>
+        <v>-2.526703794982018</v>
       </c>
       <c r="G44">
-        <v>-1.571808446167822</v>
+        <v>-2.644292779070116</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.268785049696382</v>
       </c>
       <c r="E45">
-        <v>-16.88270112265762</v>
+        <v>-18.7251651143664</v>
       </c>
       <c r="F45">
-        <v>-2.819752017600789</v>
+        <v>-2.612705727108066</v>
       </c>
       <c r="G45">
-        <v>-1.664324951808295</v>
+        <v>-2.658849247806292</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.848958201893279</v>
       </c>
       <c r="E46">
-        <v>-16.33779890226266</v>
+        <v>-18.48790930415653</v>
       </c>
       <c r="F46">
-        <v>-2.463930113197872</v>
+        <v>-2.495678122277566</v>
       </c>
       <c r="G46">
-        <v>-1.027981819886205</v>
+        <v>-2.071005608034524</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.393287846621051</v>
       </c>
       <c r="E47">
-        <v>-15.79315027641213</v>
+        <v>-18.29494649821569</v>
       </c>
       <c r="F47">
-        <v>-2.586724811886662</v>
+        <v>-2.764319327740251</v>
       </c>
       <c r="G47">
-        <v>-1.651417134750677</v>
+        <v>-2.239376643616318</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.921799242018047</v>
       </c>
       <c r="E48">
-        <v>-15.68488804831076</v>
+        <v>-17.37905357321635</v>
       </c>
       <c r="F48">
-        <v>-2.40566440681976</v>
+        <v>-3.116810366816511</v>
       </c>
       <c r="G48">
-        <v>-1.727460365787736</v>
+        <v>-1.425032099138695</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.461523579296603</v>
       </c>
       <c r="E49">
-        <v>-15.34503060250911</v>
+        <v>-18.09549438902186</v>
       </c>
       <c r="F49">
-        <v>-2.961254565714403</v>
+        <v>-2.985008000989679</v>
       </c>
       <c r="G49">
-        <v>-0.7768372141860143</v>
+        <v>-1.873574603709009</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.037562771771003</v>
       </c>
       <c r="E50">
-        <v>-15.31024739365619</v>
+        <v>-17.51901059089741</v>
       </c>
       <c r="F50">
-        <v>-2.930936318771941</v>
+        <v>-3.114581230135578</v>
       </c>
       <c r="G50">
-        <v>-1.599246247597302</v>
+        <v>-1.296811359857183</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.675999523108366</v>
       </c>
       <c r="E51">
-        <v>-14.98825930628881</v>
+        <v>-16.40004277749809</v>
       </c>
       <c r="F51">
-        <v>-2.968503608856301</v>
+        <v>-3.276106246742259</v>
       </c>
       <c r="G51">
-        <v>-1.309371569633177</v>
+        <v>-1.532687729530255</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.395702477950841</v>
       </c>
       <c r="E52">
-        <v>-14.13915684442859</v>
+        <v>-17.07211813345046</v>
       </c>
       <c r="F52">
-        <v>-3.195928565825294</v>
+        <v>-3.010711413131145</v>
       </c>
       <c r="G52">
-        <v>-0.7045845577914207</v>
+        <v>-1.712413936311748</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.211269011724184</v>
       </c>
       <c r="E53">
-        <v>-14.75737958748174</v>
+        <v>-16.65452490283313</v>
       </c>
       <c r="F53">
-        <v>-3.18234251205198</v>
+        <v>-2.868696105595197</v>
       </c>
       <c r="G53">
-        <v>-0.5965548357539233</v>
+        <v>-1.847080307758221</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.132738905214596</v>
       </c>
       <c r="E54">
-        <v>-14.13411665285805</v>
+        <v>-16.45457466149846</v>
       </c>
       <c r="F54">
-        <v>-3.178080561764576</v>
+        <v>-3.269296238323844</v>
       </c>
       <c r="G54">
-        <v>-0.4612892555648418</v>
+        <v>-1.993697748601464</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.163339806209989</v>
       </c>
       <c r="E55">
-        <v>-13.5529096563436</v>
+        <v>-16.13340622792646</v>
       </c>
       <c r="F55">
-        <v>-3.434360040475284</v>
+        <v>-3.140659064343108</v>
       </c>
       <c r="G55">
-        <v>-1.194949184159347</v>
+        <v>-1.592082227050319</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.298443754487894</v>
       </c>
       <c r="E56">
-        <v>-13.50122618249406</v>
+        <v>-15.64106147686453</v>
       </c>
       <c r="F56">
-        <v>-3.373946377421714</v>
+        <v>-3.402496888326601</v>
       </c>
       <c r="G56">
-        <v>-1.094245699400257</v>
+        <v>-1.610101526420572</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.522488336605381</v>
       </c>
       <c r="E57">
-        <v>-12.97132226801251</v>
+        <v>-15.23836692573244</v>
       </c>
       <c r="F57">
-        <v>-3.305868659157442</v>
+        <v>-3.352963002741399</v>
       </c>
       <c r="G57">
-        <v>-1.307782507774327</v>
+        <v>-1.689276533537782</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.817890187010455</v>
       </c>
       <c r="E58">
-        <v>-13.2971550298124</v>
+        <v>-15.51852549869097</v>
       </c>
       <c r="F58">
-        <v>-3.039345589143715</v>
+        <v>-3.297870771883413</v>
       </c>
       <c r="G58">
-        <v>-1.826160970495567</v>
+        <v>-1.699281002157459</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.159476409333392</v>
       </c>
       <c r="E59">
-        <v>-11.78900110324588</v>
+        <v>-15.2988582815269</v>
       </c>
       <c r="F59">
-        <v>-3.194571700019509</v>
+        <v>-3.185593025740565</v>
       </c>
       <c r="G59">
-        <v>-1.056998751537917</v>
+        <v>-1.711864385752229</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.5230216655237</v>
       </c>
       <c r="E60">
-        <v>-11.53936897357305</v>
+        <v>-14.42277517152898</v>
       </c>
       <c r="F60">
-        <v>-3.225117747997741</v>
+        <v>-3.290236537899212</v>
       </c>
       <c r="G60">
-        <v>-1.119422398226415</v>
+        <v>-1.714016240352755</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.880895185476722</v>
       </c>
       <c r="E61">
-        <v>-11.44422120619789</v>
+        <v>-14.31861121240455</v>
       </c>
       <c r="F61">
-        <v>-3.367892668442055</v>
+        <v>-3.61735385506032</v>
       </c>
       <c r="G61">
-        <v>-1.431560494942138</v>
+        <v>-2.395641014160996</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.210440219344475</v>
       </c>
       <c r="E62">
-        <v>-10.88579696241603</v>
+        <v>-14.62395262931974</v>
       </c>
       <c r="F62">
-        <v>-3.702153826084906</v>
+        <v>-3.386762049510425</v>
       </c>
       <c r="G62">
-        <v>-1.313324361007067</v>
+        <v>-2.009439392640698</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.49373008323831</v>
       </c>
       <c r="E63">
-        <v>-12.72552122735017</v>
+        <v>-14.78680561158358</v>
       </c>
       <c r="F63">
-        <v>-3.339838349611444</v>
+        <v>-3.497076564908638</v>
       </c>
       <c r="G63">
-        <v>-2.214941506990957</v>
+        <v>-2.519174020958901</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.724379103625026</v>
       </c>
       <c r="E64">
-        <v>-11.07269161318659</v>
+        <v>-13.80459771321591</v>
       </c>
       <c r="F64">
-        <v>-3.707665782783134</v>
+        <v>-3.709834448643663</v>
       </c>
       <c r="G64">
-        <v>-2.082006550861523</v>
+        <v>-2.066139106091796</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.901671795414122</v>
       </c>
       <c r="E65">
-        <v>-11.36968252403164</v>
+        <v>-14.37308875471683</v>
       </c>
       <c r="F65">
-        <v>-3.832723581216372</v>
+        <v>-3.472070638120329</v>
       </c>
       <c r="G65">
-        <v>-1.700572114917775</v>
+        <v>-2.217831613246741</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.027956235051208</v>
       </c>
       <c r="E66">
-        <v>-11.47936216449741</v>
+        <v>-14.10527933037721</v>
       </c>
       <c r="F66">
-        <v>-3.291643105749166</v>
+        <v>-3.695572447069664</v>
       </c>
       <c r="G66">
-        <v>-2.301376540475789</v>
+        <v>-2.205863991122276</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.109477955825984</v>
       </c>
       <c r="E67">
-        <v>-10.26889653377312</v>
+        <v>-13.91213538547606</v>
       </c>
       <c r="F67">
-        <v>-3.366810820613999</v>
+        <v>-3.542756056968614</v>
       </c>
       <c r="G67">
-        <v>-2.588698787829135</v>
+        <v>-2.438105381793228</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.152417237307972</v>
       </c>
       <c r="E68">
-        <v>-11.02807255878902</v>
+        <v>-13.65550223498737</v>
       </c>
       <c r="F68">
-        <v>-3.683450946864498</v>
+        <v>-3.669643718994636</v>
       </c>
       <c r="G68">
-        <v>-1.83659581003535</v>
+        <v>-2.818417542799163</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.162786739893559</v>
       </c>
       <c r="E69">
-        <v>-10.5078731641059</v>
+        <v>-13.13133589707354</v>
       </c>
       <c r="F69">
-        <v>-3.749887669303825</v>
+        <v>-3.601591680119852</v>
       </c>
       <c r="G69">
-        <v>-1.726003725750456</v>
+        <v>-2.094325090813151</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.140386962565492</v>
       </c>
       <c r="E70">
-        <v>-11.55985126150975</v>
+        <v>-13.67710305600396</v>
       </c>
       <c r="F70">
-        <v>-3.857041134692955</v>
+        <v>-3.824552565155158</v>
       </c>
       <c r="G70">
-        <v>-1.797034790841059</v>
+        <v>-2.59767036624056</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.087157101587907</v>
       </c>
       <c r="E71">
-        <v>-11.20083384218164</v>
+        <v>-13.82073719457925</v>
       </c>
       <c r="F71">
-        <v>-4.103619602749478</v>
+        <v>-4.132084791811877</v>
       </c>
       <c r="G71">
-        <v>-1.248553537531226</v>
+        <v>-1.885373388010971</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.004309653684244</v>
       </c>
       <c r="E72">
-        <v>-11.19787222018062</v>
+        <v>-13.12775387413347</v>
       </c>
       <c r="F72">
-        <v>-4.132135322223448</v>
+        <v>-4.139141653716326</v>
       </c>
       <c r="G72">
-        <v>-1.318419290592006</v>
+        <v>-1.887631180068754</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.899082301187685</v>
       </c>
       <c r="E73">
-        <v>-10.484909272413</v>
+        <v>-13.2109555270764</v>
       </c>
       <c r="F73">
-        <v>-3.967441800301059</v>
+        <v>-3.8430881141602</v>
       </c>
       <c r="G73">
-        <v>-1.100479456650705</v>
+        <v>-2.291928243506709</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.776046989822724</v>
       </c>
       <c r="E74">
-        <v>-11.1006187123919</v>
+        <v>-13.27660028629159</v>
       </c>
       <c r="F74">
-        <v>-4.008902417178577</v>
+        <v>-3.959757035905288</v>
       </c>
       <c r="G74">
-        <v>-1.958159042237388</v>
+        <v>-1.584441487945681</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.64025670384051</v>
       </c>
       <c r="E75">
-        <v>-10.8052489952416</v>
+        <v>-13.8672899073781</v>
       </c>
       <c r="F75">
-        <v>-4.327775821947024</v>
+        <v>-4.096672085342198</v>
       </c>
       <c r="G75">
-        <v>-1.029948283936532</v>
+        <v>-1.468483009341629</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.496476683887716</v>
       </c>
       <c r="E76">
-        <v>-10.9718606109318</v>
+        <v>-14.06098179763418</v>
       </c>
       <c r="F76">
-        <v>-4.538646684738472</v>
+        <v>-4.290243323293581</v>
       </c>
       <c r="G76">
-        <v>-1.294791927078227</v>
+        <v>-1.472892655999938</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.348325137994822</v>
       </c>
       <c r="E77">
-        <v>-12.71317207873125</v>
+        <v>-14.59337637281995</v>
       </c>
       <c r="F77">
-        <v>-4.232169798152919</v>
+        <v>-4.293043205115044</v>
       </c>
       <c r="G77">
-        <v>-1.306431805194305</v>
+        <v>-1.687631192404764</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.197468224472725</v>
       </c>
       <c r="E78">
-        <v>-11.74194572983218</v>
+        <v>-15.35378414276593</v>
       </c>
       <c r="F78">
-        <v>-4.334237916056263</v>
+        <v>-4.558365970762114</v>
       </c>
       <c r="G78">
-        <v>-1.443594327977388</v>
+        <v>-1.412869154827413</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.043251421145447</v>
       </c>
       <c r="E79">
-        <v>-13.11418203753248</v>
+        <v>-15.66654320010569</v>
       </c>
       <c r="F79">
-        <v>-4.505479682297782</v>
+        <v>-4.667617690782535</v>
       </c>
       <c r="G79">
-        <v>-1.218947328773524</v>
+        <v>-1.219119477141566</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.891111499598221</v>
       </c>
       <c r="E80">
-        <v>-13.59190434602365</v>
+        <v>-16.32136054161482</v>
       </c>
       <c r="F80">
-        <v>-4.775161317218384</v>
+        <v>-4.671094348772085</v>
       </c>
       <c r="G80">
-        <v>-0.7849480507572287</v>
+        <v>-1.039830262371257</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.74600238604377</v>
       </c>
       <c r="E81">
-        <v>-13.18674630503139</v>
+        <v>-17.44501532561208</v>
       </c>
       <c r="F81">
-        <v>-4.636837214829312</v>
+        <v>-4.629413386165422</v>
       </c>
       <c r="G81">
-        <v>-0.466553022972283</v>
+        <v>-0.7994416191281579</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.615075368734611</v>
       </c>
       <c r="E82">
-        <v>-15.71433671478264</v>
+        <v>-18.05062626855386</v>
       </c>
       <c r="F82">
-        <v>-4.624453122157458</v>
+        <v>-4.659637199223964</v>
       </c>
       <c r="G82">
-        <v>-0.8700356922075768</v>
+        <v>-0.9600494254203603</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.498736196576175</v>
       </c>
       <c r="E83">
-        <v>-17.301507984309</v>
+        <v>-17.91160211651838</v>
       </c>
       <c r="F83">
-        <v>-4.656519224319827</v>
+        <v>-4.962652338433219</v>
       </c>
       <c r="G83">
-        <v>-0.7042369505097972</v>
+        <v>-0.872723855185465</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.395969254319752</v>
       </c>
       <c r="E84">
-        <v>-16.64146931226902</v>
+        <v>-18.86717805924694</v>
       </c>
       <c r="F84">
-        <v>-5.127588572004628</v>
+        <v>-4.878013070684776</v>
       </c>
       <c r="G84">
-        <v>-0.5861100645775227</v>
+        <v>-1.106805909176252</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.301082257479038</v>
       </c>
       <c r="E85">
-        <v>-17.90135870831303</v>
+        <v>-19.77666319352543</v>
       </c>
       <c r="F85">
-        <v>-5.414736333613257</v>
+        <v>-5.343005515102639</v>
       </c>
       <c r="G85">
-        <v>-0.4766435657759816</v>
+        <v>-0.9988126031396867</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.207127763832359</v>
       </c>
       <c r="E86">
-        <v>-18.34444271911953</v>
+        <v>-20.3940662827832</v>
       </c>
       <c r="F86">
-        <v>-5.666431627116872</v>
+        <v>-5.220484177656773</v>
       </c>
       <c r="G86">
-        <v>-0.9148538577182301</v>
+        <v>-0.4786894829192512</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.10322991693969</v>
       </c>
       <c r="E87">
-        <v>-20.19451001868719</v>
+        <v>-22.38135993020529</v>
       </c>
       <c r="F87">
-        <v>-5.598695196222554</v>
+        <v>-5.479889914945646</v>
       </c>
       <c r="G87">
-        <v>-1.180151045598805</v>
+        <v>-1.629262964001874</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.977511075058289</v>
       </c>
       <c r="E88">
-        <v>-21.36966713757367</v>
+        <v>-22.43504046109221</v>
       </c>
       <c r="F88">
-        <v>-5.395796541315649</v>
+        <v>-5.293964508122103</v>
       </c>
       <c r="G88">
-        <v>-0.4705951990757332</v>
+        <v>-0.8106908528706015</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.823316347447364</v>
       </c>
       <c r="E89">
-        <v>-22.95713728638454</v>
+        <v>-24.85466299355258</v>
       </c>
       <c r="F89">
-        <v>-5.856239591957338</v>
+        <v>-5.413458162710738</v>
       </c>
       <c r="G89">
-        <v>-0.9213359058841231</v>
+        <v>-0.8115052470732622</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.638772603604566</v>
       </c>
       <c r="E90">
-        <v>-24.92528907417621</v>
+        <v>-25.71606026234362</v>
       </c>
       <c r="F90">
-        <v>-5.405796592602245</v>
+        <v>-5.746398902713525</v>
       </c>
       <c r="G90">
-        <v>-0.7211273538511588</v>
+        <v>-0.8335766541835832</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.429333412167364</v>
       </c>
       <c r="E91">
-        <v>-25.53384352522298</v>
+        <v>-27.82995645759815</v>
       </c>
       <c r="F91">
-        <v>-5.890852095515912</v>
+        <v>-5.401947169281435</v>
       </c>
       <c r="G91">
-        <v>-0.4431408449185572</v>
+        <v>-1.482294605331469</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.20334894701516</v>
       </c>
       <c r="E92">
-        <v>-27.43252852173699</v>
+        <v>-29.5121713395975</v>
       </c>
       <c r="F92">
-        <v>-5.620306473394191</v>
+        <v>-5.490221313193362</v>
       </c>
       <c r="G92">
-        <v>-1.390953343357437</v>
+        <v>-1.641571572316884</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.97907312420668</v>
       </c>
       <c r="E93">
-        <v>-30.45576041162775</v>
+        <v>-31.99538496831058</v>
       </c>
       <c r="F93">
-        <v>-5.654966193894725</v>
+        <v>-5.727034986305685</v>
       </c>
       <c r="G93">
-        <v>-1.232358348753112</v>
+        <v>-2.070965881488053</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.777843097118796</v>
       </c>
       <c r="E94">
-        <v>-32.24469557632887</v>
+        <v>-33.41625708685326</v>
       </c>
       <c r="F94">
-        <v>-5.947992878961021</v>
+        <v>-5.527589795101051</v>
       </c>
       <c r="G94">
-        <v>-1.347691134250241</v>
+        <v>-2.342599453530794</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.624582380172514</v>
       </c>
       <c r="E95">
-        <v>-33.18098701249576</v>
+        <v>-36.07743521559378</v>
       </c>
       <c r="F95">
-        <v>-5.482809081673112</v>
+        <v>-5.519738528857316</v>
       </c>
       <c r="G95">
-        <v>-1.919862651439099</v>
+        <v>-2.209449311941306</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.54718354964595</v>
       </c>
       <c r="E96">
-        <v>-37.02521539031814</v>
+        <v>-36.95410702721269</v>
       </c>
       <c r="F96">
-        <v>-5.936787553103353</v>
+        <v>-5.396354860945136</v>
       </c>
       <c r="G96">
-        <v>-2.273779832860424</v>
+        <v>-3.01788453263133</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.557258691611869</v>
       </c>
       <c r="E97">
-        <v>-38.2574448671233</v>
+        <v>-41.04648219523339</v>
       </c>
       <c r="F97">
-        <v>-5.774716642378227</v>
+        <v>-5.606263989181933</v>
       </c>
       <c r="G97">
-        <v>-3.029646900932361</v>
+        <v>-3.175449947572942</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.68428436079886</v>
       </c>
       <c r="E98">
-        <v>-41.12982649510755</v>
+        <v>-42.56369306981524</v>
       </c>
       <c r="F98">
-        <v>-5.608818674252167</v>
+        <v>-5.325169108185561</v>
       </c>
       <c r="G98">
-        <v>-3.400858372250839</v>
+        <v>-4.311900641385034</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.910103553516302</v>
       </c>
       <c r="E99">
-        <v>-43.59742820967919</v>
+        <v>-44.75826629375343</v>
       </c>
       <c r="F99">
-        <v>-6.427372408430707</v>
+        <v>-5.426627547680444</v>
       </c>
       <c r="G99">
-        <v>-4.255899453042723</v>
+        <v>-4.520421973267108</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.268703710473972</v>
       </c>
       <c r="E100">
-        <v>-46.21002260502842</v>
+        <v>-46.84763400954541</v>
       </c>
       <c r="F100">
-        <v>-5.554997987357478</v>
+        <v>-5.455224447159888</v>
       </c>
       <c r="G100">
-        <v>-4.759754552483179</v>
+        <v>-4.634450403821765</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.68592877183869</v>
       </c>
       <c r="E101">
-        <v>-48.17046466582203</v>
+        <v>-48.40746008877645</v>
       </c>
       <c r="F101">
-        <v>-6.031816204817707</v>
+        <v>-5.109453952822541</v>
       </c>
       <c r="G101">
-        <v>-4.081059611477193</v>
+        <v>-4.219652289933243</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.250266896817248</v>
       </c>
       <c r="E102">
-        <v>-50.57921206795298</v>
+        <v>-51.37537666866353</v>
       </c>
       <c r="F102">
-        <v>-5.989056707852599</v>
+        <v>-5.181885570155927</v>
       </c>
       <c r="G102">
-        <v>-5.202258621989863</v>
+        <v>-5.710940496826577</v>
       </c>
     </row>
   </sheetData>
